--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5243AEED-CC93-4177-80E3-1E6EE6773A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEC2F71-F042-4BBE-A5EF-A353A8EF2601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="46">
   <si>
     <t>日付</t>
   </si>
@@ -198,9 +198,6 @@
   <si>
     <t>・日付は必ず「日付」として入力してください（例: 2026/9/10 や 2026-9-10 と入力すればExcelが自動で</t>
     <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1,178,871	</t>
   </si>
 </sst>
 </file>
@@ -9944,8 +9941,8 @@
       <c r="B694" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C694" s="7" t="s">
-        <v>46</v>
+      <c r="C694" s="7">
+        <v>1178871</v>
       </c>
       <c r="D694" s="7"/>
       <c r="E694" s="5"/>

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FA3CFA-828A-4382-B93F-48EE1C15A28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584F0FAC-83B1-47BD-A73F-9C00AAFC9BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="46">
   <si>
     <t>日付</t>
   </si>
@@ -1261,392 +1261,212 @@
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="7">
-        <v>849487</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="7">
-        <v>396130</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="7">
-        <v>478083</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="7">
-        <v>898303</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="7">
-        <v>3872497</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="7">
-        <v>579867</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="7">
-        <v>785883</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1122898</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="7">
-        <v>860076</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" s="7">
-        <v>3710768</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="7">
-        <v>872777</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="7">
-        <v>440485</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="7">
-        <v>768409</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="7">
-        <v>467858</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C50" s="7">
-        <v>1529518</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" s="7">
-        <v>643653</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="7">
-        <v>509543</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" s="7">
-        <v>949130</v>
-      </c>
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C54" s="7">
-        <v>674102</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="7">
-        <v>2851018</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1217542</v>
-      </c>
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C57" s="7">
-        <v>827453</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1231375</v>
-      </c>
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C59" s="7">
-        <v>733905</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="7">
-        <v>808726</v>
-      </c>
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="7">
-        <v>312018</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="7">
-        <v>404092</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C63" s="7">
-        <v>451507</v>
-      </c>
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="7">
-        <v>566097</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C65" s="7">
-        <v>1764428</v>
-      </c>
+      <c r="A65" s="6"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,23 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,30 +220,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,16 +240,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,14 +272,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -316,17 +294,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,9 +309,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,20 +604,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,22 +638,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +657,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22981,8 +22981,19 @@
         <v>775403</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1724">
+        <v>481913</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,31 +203,54 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +264,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,29 +309,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -296,21 +319,22 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,30 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +392,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,31 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +440,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,67 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,20 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,6 +601,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -615,6 +641,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,199 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22992,8 +22992,19 @@
         <v>481913</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1725">
+        <v>1586170</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,13 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -219,7 +212,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,10 +242,78 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,14 +326,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,75 +346,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,25 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,37 +446,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,19 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -597,15 +621,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,21 +641,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23003,8 +23003,19 @@
         <v>1586170</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1726">
+        <v>758045</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,31 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,8 +227,38 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,24 +278,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,32 +318,17 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,18 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +464,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,91 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,6 +587,45 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,41 +645,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -654,17 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23014,8 +23014,19 @@
         <v>758045</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1727">
+        <v>554252</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,106 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,37 +319,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -258,28 +326,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,57 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,97 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +571,62 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,47 +649,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,28 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23025,8 +23025,19 @@
         <v>554252</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1728">
+        <v>816038</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -204,76 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,6 +220,75 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,16 +317,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +476,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -581,6 +599,30 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -601,17 +643,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,51 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23036,8 +23036,19 @@
         <v>816038</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1729">
+        <v>471203</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,44 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -257,7 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,15 +227,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,10 +271,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,8 +309,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,15 +319,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,67 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,17 +574,49 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,8 +639,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,205 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23047,8 +23047,19 @@
         <v>471203</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1730">
+        <v>757571</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,8 +241,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,7 +258,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,31 +280,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,32 +295,39 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,32 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,31 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,18 +574,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -621,6 +610,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -639,17 +637,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23058,8 +23058,19 @@
         <v>757571</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1731">
+        <v>576310</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -222,53 +222,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,9 +239,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,31 +285,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +317,33 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,163 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -613,8 +613,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,19 +637,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +657,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23069,8 +23069,19 @@
         <v>576310</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1732">
+        <v>833239</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,62 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,53 +272,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -286,7 +294,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -294,30 +318,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,16 +333,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,37 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +446,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,6 +604,15 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -636,9 +636,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,33 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23080,8 +23080,19 @@
         <v>833239</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1733">
+        <v>771414</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,7 +205,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,16 +226,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,6 +235,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,23 +255,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,12 +286,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -294,16 +309,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,30 +340,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +416,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +452,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,43 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,17 +634,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,58 +668,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -704,115 +698,121 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23091,8 +23091,19 @@
         <v>771414</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1734">
+        <v>1009286</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,31 +239,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,14 +255,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,22 +295,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,7 +317,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -317,25 +325,17 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +404,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,49 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,11 +619,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,8 +637,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -651,15 +660,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23102,8 +23102,16 @@
         <v>1009286</v>
       </c>
     </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,6 +205,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -219,6 +226,44 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -226,8 +271,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,6 +303,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,93 +334,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,19 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,12 +392,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -410,13 +404,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +482,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,20 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,6 +596,39 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -621,17 +643,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,43 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23124,8 +23124,19 @@
         <v>1064562</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1737">
+        <v>342400</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,16 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,9 +218,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,24 +255,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,45 +286,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,6 +311,29 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +416,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,25 +470,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,109 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,23 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,24 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,11 +612,44 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23135,8 +23135,19 @@
         <v>342400</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1738">
+        <v>404500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,31 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,11 +247,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -241,29 +263,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -278,10 +303,17 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -293,48 +325,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,25 +422,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,19 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,37 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,9 +618,38 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,199 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23146,8 +23146,19 @@
         <v>404500</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1739">
+        <v>691284</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,24 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +241,92 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,93 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +374,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +482,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,31 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,67 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,16 +571,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -601,17 +625,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,41 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,142 +674,142 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23157,8 +23157,19 @@
         <v>691284</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1740">
+        <v>2729068</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,37 +227,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,31 +249,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,7 +273,22 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,14 +296,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,8 +310,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,31 +464,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,60 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -644,7 +590,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +644,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23168,8 +23168,19 @@
         <v>2729068</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1741">
+        <v>772849</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,105 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,90 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,21 +342,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,43 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +446,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,17 +591,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,29 +617,39 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23179,8 +23179,19 @@
         <v>772849</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1742">
+        <v>970917</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,38 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -217,6 +249,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -225,23 +265,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,8 +279,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,77 +334,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,55 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,85 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -582,20 +597,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,22 +631,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23190,8 +23190,19 @@
         <v>970917</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1743">
+        <v>812796</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -167,8 +167,8 @@
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,50 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -211,9 +255,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,21 +307,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -257,17 +331,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -276,74 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,43 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,25 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -582,6 +597,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,59 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23201,8 +23201,19 @@
         <v>812796</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1744">
+        <v>400345</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,13 +204,95 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -227,21 +309,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,75 +317,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,15 +340,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +428,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,36 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -625,6 +595,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -636,11 +632,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,173 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23212,8 +23212,19 @@
         <v>400345</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1745">
+        <v>508565</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -210,8 +210,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,8 +278,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,110 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,25 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +404,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -595,32 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -630,11 +619,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +649,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23223,8 +23223,19 @@
         <v>508565</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1746">
+        <v>481425</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,17 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,14 +228,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,44 +258,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,6 +277,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -300,7 +293,31 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -317,31 +334,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,37 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,43 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,12 +398,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -476,7 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +428,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +458,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,15 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -613,8 +604,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,21 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -659,173 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23234,8 +23234,19 @@
         <v>481425</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1747">
+        <v>480227</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,14 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -211,24 +219,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,6 +240,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -248,8 +293,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,27 +317,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -297,53 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +440,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,55 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,55 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,26 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,9 +606,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,28 +645,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23245,8 +23245,19 @@
         <v>480227</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1748">
+        <v>480227</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,18 +204,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,22 +234,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,9 +256,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,37 +302,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,9 +316,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,37 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +464,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,31 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -588,9 +612,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,32 +650,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,175 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23256,8 +23256,19 @@
         <v>480227</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1749">
+        <v>336317</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,19 +203,17 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,21 +232,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -263,10 +252,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -280,7 +293,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,35 +310,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,18 +324,26 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +440,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,31 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,35 +621,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,6 +644,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -677,155 +677,155 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23267,8 +23267,19 @@
         <v>336317</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1750">
+        <v>672434</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,22 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,13 +219,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -246,7 +226,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,37 +250,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,6 +264,21 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -307,16 +286,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,7 +318,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +326,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +410,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,31 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,25 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,45 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -589,58 +628,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +657,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23278,8 +23278,19 @@
         <v>672434</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1751">
+        <v>2895324</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,15 +210,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,22 +227,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,22 +249,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,25 +262,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,8 +293,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +336,14 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,37 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -589,23 +604,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,24 +621,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +642,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23289,8 +23289,19 @@
         <v>2895324</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1752">
+        <v>852965</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -212,7 +212,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,22 +255,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -256,38 +263,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,6 +277,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -309,23 +315,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +446,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,31 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,121 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,16 +571,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -604,8 +604,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,35 +634,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +659,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23300,8 +23300,30 @@
         <v>852965</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1753">
+        <v>852965</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1754">
+        <v>680020</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,13 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -220,29 +213,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,76 +227,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,6 +257,90 @@
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,37 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,31 +398,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +446,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,43 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,9 +597,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,6 +611,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,37 +645,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23322,8 +23322,19 @@
         <v>680020</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1755">
+        <v>630801</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,84 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,7 +219,52 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,14 +272,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,7 +325,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,19 +368,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,61 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +488,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,23 +600,26 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,15 +639,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,151 +653,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23333,8 +23333,19 @@
         <v>630801</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1756">
+        <v>342062</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,14 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,8 +218,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,14 +228,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,31 +249,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,8 +272,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,52 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +392,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,59 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,164 +615,217 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23344,8 +23344,19 @@
         <v>342062</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1757">
+        <v>639490</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,75 +219,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,23 +232,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,8 +254,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +291,59 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,43 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +452,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,55 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,25 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -582,21 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,15 +631,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -654,17 +645,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23355,8 +23355,19 @@
         <v>639490</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1758">
+        <v>358981</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,7 +218,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,16 +247,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,9 +269,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,47 +309,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,7 +332,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -326,22 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,55 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +446,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,37 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,21 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -602,16 +587,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,24 +617,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +644,188 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23366,8 +23366,19 @@
         <v>358981</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1759">
+        <v>244312</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -217,16 +224,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,7 +241,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,45 +262,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,10 +279,41 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,24 +326,22 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +374,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,37 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,43 +476,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,21 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -621,6 +606,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -632,24 +632,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +650,182 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23377,8 +23377,19 @@
         <v>244312</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1760">
+        <v>348130</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,76 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,8 +300,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,103 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +410,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,31 +464,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,31 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -595,17 +619,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -621,17 +634,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,18 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23388,8 +23388,30 @@
         <v>348130</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1761">
+        <v>348130</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1762">
+        <v>638768</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -219,17 +211,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -241,9 +226,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,14 +250,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,6 +293,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -309,31 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +329,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,31 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +470,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -582,15 +611,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,15 +630,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -630,15 +641,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23410,8 +23410,19 @@
         <v>638768</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1763">
+        <v>2707437</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -204,31 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,30 +225,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,9 +242,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,11 +264,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,15 +280,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -340,8 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,31 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +398,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,67 +446,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +500,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,35 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,17 +601,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +636,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23421,8 +23421,19 @@
         <v>2707437</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1764">
+        <v>1086292</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,22 +210,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -234,7 +218,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,11 +263,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -272,38 +286,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,6 +308,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -333,15 +325,23 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +476,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -603,10 +588,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -616,7 +599,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +643,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23432,8 +23432,19 @@
         <v>1086292</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1765">
+        <v>654436</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,6 +203,66 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -211,7 +271,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,44 +302,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,30 +323,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -325,25 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,55 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,13 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +494,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,78 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +596,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23443,8 +23443,19 @@
         <v>654436</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1766">
+        <v>332072</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -167,8 +167,8 @@
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,16 +204,29 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,24 +241,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,14 +256,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,21 +287,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,32 +331,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +398,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +470,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,37 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,24 +603,44 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -686,146 +686,146 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23454,8 +23454,19 @@
         <v>332072</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1767">
+        <v>348945</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/ドリクラ.xlsx
+++ b/dashboard/data/incoming/ドリクラ.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,15 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,7 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,16 +232,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,6 +256,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -270,40 +300,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -312,6 +313,14 @@
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,25 +334,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,49 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -603,20 +603,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -632,15 +621,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +643,28 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23465,8 +23465,19 @@
         <v>348945</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1768">
+        <v>605207</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
